--- a/loss_triangle.xlsx
+++ b/loss_triangle.xlsx
@@ -451,22 +451,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44397.45</v>
+        <v>142921.44</v>
       </c>
       <c r="C2" t="n">
-        <v>23242.79</v>
+        <v>59263.37</v>
       </c>
       <c r="D2" t="n">
-        <v>11532.95</v>
+        <v>36333.17</v>
       </c>
       <c r="E2" t="n">
-        <v>7141.09</v>
+        <v>22243.24</v>
       </c>
       <c r="F2" t="n">
-        <v>7272.719999999999</v>
+        <v>13569.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1341.55</v>
+        <v>6726.23</v>
       </c>
     </row>
     <row r="3">
@@ -476,22 +476,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29025.33</v>
+        <v>132153.1</v>
       </c>
       <c r="C3" t="n">
-        <v>15673.63</v>
+        <v>55271.47</v>
       </c>
       <c r="D3" t="n">
-        <v>11351.33</v>
+        <v>38187.29</v>
       </c>
       <c r="E3" t="n">
-        <v>473.02</v>
+        <v>21700.66</v>
       </c>
       <c r="F3" t="n">
-        <v>2959.21</v>
+        <v>7848.92</v>
       </c>
       <c r="G3" t="n">
-        <v>1627.44</v>
+        <v>3771.12</v>
       </c>
     </row>
     <row r="4">
@@ -501,21 +501,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42286.71</v>
+        <v>149479.09</v>
       </c>
       <c r="C4" t="n">
-        <v>28459.15</v>
+        <v>64130.34</v>
       </c>
       <c r="D4" t="n">
-        <v>12171.99</v>
+        <v>28666.48</v>
       </c>
       <c r="E4" t="n">
-        <v>6790.35</v>
+        <v>10308.83</v>
       </c>
       <c r="F4" t="n">
-        <v>3775.13</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>7460.03</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5359.059999999999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -524,22 +526,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35757.69</v>
+        <v>126596.11</v>
       </c>
       <c r="C5" t="n">
-        <v>18507.67</v>
+        <v>55608</v>
       </c>
       <c r="D5" t="n">
-        <v>10505.2</v>
+        <v>33141.12</v>
       </c>
       <c r="E5" t="n">
-        <v>3847.27</v>
+        <v>14297.45</v>
       </c>
       <c r="F5" t="n">
-        <v>5001.84</v>
+        <v>8974.16</v>
       </c>
       <c r="G5" t="n">
-        <v>1406.32</v>
+        <v>3608.26</v>
       </c>
     </row>
     <row r="6">
@@ -549,22 +551,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48731.81</v>
+        <v>158682.8</v>
       </c>
       <c r="C6" t="n">
-        <v>18257.97</v>
+        <v>54152.73</v>
       </c>
       <c r="D6" t="n">
-        <v>14370.97</v>
+        <v>24533.54</v>
       </c>
       <c r="E6" t="n">
-        <v>9887.540000000001</v>
+        <v>26311.51</v>
       </c>
       <c r="F6" t="n">
-        <v>2522.33</v>
+        <v>6793.15</v>
       </c>
       <c r="G6" t="n">
-        <v>5339.04</v>
+        <v>3785.17</v>
       </c>
     </row>
     <row r="7">
@@ -574,19 +576,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45711.94</v>
+        <v>151382.77</v>
       </c>
       <c r="C7" t="n">
-        <v>17621</v>
+        <v>78357.27</v>
       </c>
       <c r="D7" t="n">
-        <v>9381.780000000001</v>
+        <v>29260.19</v>
       </c>
       <c r="E7" t="n">
-        <v>3113.22</v>
+        <v>13088.76</v>
       </c>
       <c r="F7" t="n">
-        <v>2236.69</v>
+        <v>11629.98</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -597,16 +599,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39228.47</v>
+        <v>140891.01</v>
       </c>
       <c r="C8" t="n">
-        <v>17550.04</v>
+        <v>54404.41</v>
       </c>
       <c r="D8" t="n">
-        <v>15031.28</v>
+        <v>23348.08</v>
       </c>
       <c r="E8" t="n">
-        <v>5356.65</v>
+        <v>21402.86</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -618,13 +620,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34728.45</v>
+        <v>144749.95</v>
       </c>
       <c r="C9" t="n">
-        <v>22379.86</v>
+        <v>60035.15</v>
       </c>
       <c r="D9" t="n">
-        <v>12764.34</v>
+        <v>22974.69</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -637,10 +639,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35380.06</v>
+        <v>164470.01</v>
       </c>
       <c r="C10" t="n">
-        <v>21853.13</v>
+        <v>41650.44</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -654,7 +656,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44676.73</v>
+        <v>156678.17</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -734,22 +736,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44397.45</v>
+        <v>142921.44</v>
       </c>
       <c r="C2" t="n">
-        <v>67640.23999999999</v>
+        <v>202184.81</v>
       </c>
       <c r="D2" t="n">
-        <v>79173.18999999999</v>
+        <v>238517.98</v>
       </c>
       <c r="E2" t="n">
-        <v>86314.27999999998</v>
+        <v>260761.22</v>
       </c>
       <c r="F2" t="n">
-        <v>93586.99999999999</v>
+        <v>274330.79</v>
       </c>
       <c r="G2" t="n">
-        <v>94928.54999999999</v>
+        <v>281057.02</v>
       </c>
     </row>
     <row r="3">
@@ -759,22 +761,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29025.33</v>
+        <v>132153.1</v>
       </c>
       <c r="C3" t="n">
-        <v>44698.96</v>
+        <v>187424.57</v>
       </c>
       <c r="D3" t="n">
-        <v>56050.29</v>
+        <v>225611.86</v>
       </c>
       <c r="E3" t="n">
-        <v>56523.31</v>
+        <v>247312.52</v>
       </c>
       <c r="F3" t="n">
-        <v>59482.52</v>
+        <v>255161.44</v>
       </c>
       <c r="G3" t="n">
-        <v>61109.96</v>
+        <v>258932.56</v>
       </c>
     </row>
     <row r="4">
@@ -784,21 +786,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42286.71</v>
+        <v>149479.09</v>
       </c>
       <c r="C4" t="n">
-        <v>70745.86</v>
+        <v>213609.43</v>
       </c>
       <c r="D4" t="n">
-        <v>82917.85000000001</v>
+        <v>242275.91</v>
       </c>
       <c r="E4" t="n">
-        <v>89708.20000000001</v>
+        <v>252584.74</v>
       </c>
       <c r="F4" t="n">
-        <v>93483.33000000002</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>260044.77</v>
+      </c>
+      <c r="G4" t="n">
+        <v>265403.83</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -807,22 +811,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35757.69</v>
+        <v>126596.11</v>
       </c>
       <c r="C5" t="n">
-        <v>54265.36</v>
+        <v>182204.11</v>
       </c>
       <c r="D5" t="n">
-        <v>64770.56</v>
+        <v>215345.23</v>
       </c>
       <c r="E5" t="n">
-        <v>68617.83</v>
+        <v>229642.68</v>
       </c>
       <c r="F5" t="n">
-        <v>73619.67</v>
+        <v>238616.84</v>
       </c>
       <c r="G5" t="n">
-        <v>75025.99000000001</v>
+        <v>242225.1</v>
       </c>
     </row>
     <row r="6">
@@ -832,22 +836,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48731.81</v>
+        <v>158682.8</v>
       </c>
       <c r="C6" t="n">
-        <v>66989.78</v>
+        <v>212835.53</v>
       </c>
       <c r="D6" t="n">
-        <v>81360.75</v>
+        <v>237369.07</v>
       </c>
       <c r="E6" t="n">
-        <v>91248.29000000001</v>
+        <v>263680.58</v>
       </c>
       <c r="F6" t="n">
-        <v>93770.62000000001</v>
+        <v>270473.73</v>
       </c>
       <c r="G6" t="n">
-        <v>99109.66</v>
+        <v>274258.9</v>
       </c>
     </row>
     <row r="7">
@@ -857,19 +861,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>45711.94</v>
+        <v>151382.77</v>
       </c>
       <c r="C7" t="n">
-        <v>63332.94</v>
+        <v>229740.04</v>
       </c>
       <c r="D7" t="n">
-        <v>72714.72</v>
+        <v>259000.23</v>
       </c>
       <c r="E7" t="n">
-        <v>75827.94</v>
+        <v>272088.99</v>
       </c>
       <c r="F7" t="n">
-        <v>78064.63</v>
+        <v>283718.97</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -880,16 +884,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39228.47</v>
+        <v>140891.01</v>
       </c>
       <c r="C8" t="n">
-        <v>56778.51</v>
+        <v>195295.42</v>
       </c>
       <c r="D8" t="n">
-        <v>71809.79000000001</v>
+        <v>218643.5</v>
       </c>
       <c r="E8" t="n">
-        <v>77166.44</v>
+        <v>240046.36</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -901,13 +905,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34728.45</v>
+        <v>144749.95</v>
       </c>
       <c r="C9" t="n">
-        <v>57108.31</v>
+        <v>204785.1</v>
       </c>
       <c r="D9" t="n">
-        <v>69872.64999999999</v>
+        <v>227759.79</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -920,10 +924,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35380.06</v>
+        <v>164470.01</v>
       </c>
       <c r="C10" t="n">
-        <v>57233.19</v>
+        <v>206120.45</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -937,7 +941,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44676.73</v>
+        <v>156678.17</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -1024,19 +1028,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.523516328077401</v>
+        <v>1.414656961194905</v>
       </c>
       <c r="C2" t="n">
-        <v>1.170504273787319</v>
+        <v>1.179702767977476</v>
       </c>
       <c r="D2" t="n">
-        <v>1.090195809970522</v>
+        <v>1.093256030425882</v>
       </c>
       <c r="E2" t="n">
-        <v>1.084258595449096</v>
+        <v>1.05203829771927</v>
       </c>
       <c r="F2" t="n">
-        <v>1.014334790088367</v>
+        <v>1.024518684176865</v>
       </c>
     </row>
     <row r="3">
@@ -1046,19 +1050,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.539998339381499</v>
+        <v>1.418238164674154</v>
       </c>
       <c r="C3" t="n">
-        <v>1.253950651200833</v>
+        <v>1.203747512932803</v>
       </c>
       <c r="D3" t="n">
-        <v>1.008439207004995</v>
+        <v>1.096185812217496</v>
       </c>
       <c r="E3" t="n">
-        <v>1.052353798813268</v>
+        <v>1.031736848583323</v>
       </c>
       <c r="F3" t="n">
-        <v>1.027359970626665</v>
+        <v>1.014779349105413</v>
       </c>
     </row>
     <row r="4">
@@ -1068,18 +1072,20 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.673004591749985</v>
+        <v>1.429025491123876</v>
       </c>
       <c r="C4" t="n">
-        <v>1.172052329281176</v>
+        <v>1.134200442368111</v>
       </c>
       <c r="D4" t="n">
-        <v>1.081892499624629</v>
+        <v>1.042549958846507</v>
       </c>
       <c r="E4" t="n">
-        <v>1.042082329151627</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1.02953476128447</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.020608220653697</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1088,19 +1094,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.517585727713395</v>
+        <v>1.439255203023221</v>
       </c>
       <c r="C5" t="n">
-        <v>1.193589427951828</v>
+        <v>1.181890079208422</v>
       </c>
       <c r="D5" t="n">
-        <v>1.059398436573653</v>
+        <v>1.06639315855754</v>
       </c>
       <c r="E5" t="n">
-        <v>1.072894173424021</v>
+        <v>1.039078798418482</v>
       </c>
       <c r="F5" t="n">
-        <v>1.019102503447788</v>
+        <v>1.015121564764666</v>
       </c>
     </row>
     <row r="6">
@@ -1110,19 +1116,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.37466225859454</v>
+        <v>1.341264018532569</v>
       </c>
       <c r="C6" t="n">
-        <v>1.214524812590816</v>
+        <v>1.115269945765164</v>
       </c>
       <c r="D6" t="n">
-        <v>1.12152714914747</v>
+        <v>1.110846413140516</v>
       </c>
       <c r="E6" t="n">
-        <v>1.027642490615441</v>
+        <v>1.025762799823938</v>
       </c>
       <c r="F6" t="n">
-        <v>1.056937236844547</v>
+        <v>1.013994593855751</v>
       </c>
     </row>
     <row r="7">
@@ -1132,16 +1138,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.385479154899136</v>
+        <v>1.51761022737264</v>
       </c>
       <c r="C7" t="n">
-        <v>1.148134288412949</v>
+        <v>1.127362169868169</v>
       </c>
       <c r="D7" t="n">
-        <v>1.042814164724831</v>
+        <v>1.050535708018483</v>
       </c>
       <c r="E7" t="n">
-        <v>1.029496911033057</v>
+        <v>1.042743295125613</v>
       </c>
       <c r="F7" t="inlineStr"/>
     </row>
@@ -1152,13 +1158,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.447380180771771</v>
+        <v>1.386145361581268</v>
       </c>
       <c r="C8" t="n">
-        <v>1.264735372590792</v>
+        <v>1.119552624429185</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074594982104808</v>
+        <v>1.09788930382106</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -1170,10 +1176,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.644424384042478</v>
+        <v>1.414750747755008</v>
       </c>
       <c r="C9" t="n">
-        <v>1.223511079210714</v>
+        <v>1.112189265722946</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -1186,7 +1192,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.617667974559682</v>
+        <v>1.253240332386433</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
@@ -1236,19 +1242,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.524857659976654</v>
+        <v>1.401576278627119</v>
       </c>
       <c r="C14" t="n">
-        <v>1.205125279378303</v>
+        <v>1.146739351034034</v>
       </c>
       <c r="D14" t="n">
-        <v>1.068408892735844</v>
+        <v>1.079665197861069</v>
       </c>
       <c r="E14" t="n">
-        <v>1.051454716414418</v>
+        <v>1.036815800159183</v>
       </c>
       <c r="F14" t="n">
-        <v>1.029433625251841</v>
+        <v>1.017804482511279</v>
       </c>
     </row>
   </sheetData>
@@ -1299,13 +1305,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94928.54999999999</v>
+        <v>281057.02</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>94928.54999999999</v>
+        <v>281057.02</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1318,13 +1324,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61109.96</v>
+        <v>258932.56</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>61109.96</v>
+        <v>258932.56</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1337,16 +1343,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93483.33000000002</v>
+        <v>265403.83</v>
       </c>
       <c r="C4" t="n">
-        <v>1.029433625251841</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>96234.88330251424</v>
+        <v>265403.83</v>
       </c>
       <c r="E4" t="n">
-        <v>2751.553302514221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1356,13 +1362,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75025.99000000001</v>
+        <v>242225.1</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>75025.99000000001</v>
+        <v>242225.1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1375,13 +1381,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99109.66</v>
+        <v>274258.9</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>99109.66</v>
+        <v>274258.9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1394,16 +1400,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78064.63</v>
+        <v>283718.97</v>
       </c>
       <c r="C7" t="n">
-        <v>1.029433625251841</v>
+        <v>1.017804482511279</v>
       </c>
       <c r="D7" t="n">
-        <v>80362.35506484366</v>
+        <v>288770.439439483</v>
       </c>
       <c r="E7" t="n">
-        <v>2297.72506484366</v>
+        <v>5051.469439483015</v>
       </c>
     </row>
     <row r="8">
@@ -1413,16 +1419,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77166.44</v>
+        <v>240046.36</v>
       </c>
       <c r="C8" t="n">
-        <v>1.082402840506641</v>
+        <v>1.055275768940534</v>
       </c>
       <c r="D8" t="n">
-        <v>83525.17384778532</v>
+        <v>253315.1071303763</v>
       </c>
       <c r="E8" t="n">
-        <v>6358.733847785319</v>
+        <v>13268.74713037632</v>
       </c>
     </row>
     <row r="9">
@@ -1432,16 +1438,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69872.64999999999</v>
+        <v>227759.79</v>
       </c>
       <c r="C9" t="n">
-        <v>1.156448820319833</v>
+        <v>1.139344521871174</v>
       </c>
       <c r="D9" t="n">
-        <v>80804.14366512059</v>
+        <v>259496.869039029</v>
       </c>
       <c r="E9" t="n">
-        <v>10931.49366512059</v>
+        <v>31737.07903902899</v>
       </c>
     </row>
     <row r="10">
@@ -1451,16 +1457,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57233.19</v>
+        <v>206120.45</v>
       </c>
       <c r="C10" t="n">
-        <v>1.393665707674649</v>
+        <v>1.306531197614732</v>
       </c>
       <c r="D10" t="n">
-        <v>79763.93424382762</v>
+        <v>269302.7983913876</v>
       </c>
       <c r="E10" t="n">
-        <v>22530.74424382762</v>
+        <v>63182.34839138761</v>
       </c>
     </row>
     <row r="11">
@@ -1470,16 +1476,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44676.73</v>
+        <v>156678.17</v>
       </c>
       <c r="C11" t="n">
-        <v>2.125141829794472</v>
+        <v>1.83120313386309</v>
       </c>
       <c r="D11" t="n">
-        <v>94944.38774143359</v>
+        <v>286909.5559119341</v>
       </c>
       <c r="E11" t="n">
-        <v>50267.65774143358</v>
+        <v>130231.385911934</v>
       </c>
     </row>
     <row r="12">
@@ -1490,7 +1496,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.029433625251841</v>
+        <v>1.017804482511279</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
@@ -1503,7 +1509,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.029433625251841</v>
+        <v>1.017804482511279</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
@@ -1515,16 +1521,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>750671.1299999999</v>
+        <v>2436201.15</v>
       </c>
       <c r="C14" t="n">
-        <v>13.87539369930296</v>
+        <v>13.38576806982337</v>
       </c>
       <c r="D14" t="n">
-        <v>845809.037865525</v>
+        <v>2679672.17991221</v>
       </c>
       <c r="E14" t="n">
-        <v>95137.90786552499</v>
+        <v>243471.02991221</v>
       </c>
     </row>
   </sheetData>
